--- a/assets/constructions/examples/ctd_me1.xlsx
+++ b/assets/constructions/examples/ctd_me1.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ctd" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ctd" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AP6"/>
+  <dimension ref="A1:AU6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -639,21 +639,46 @@
           <t>cpdf</t>
         </is>
       </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>lcs</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>pricecurrency</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue_rub</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>HM END MILL Ø20 FH700SE V-MAXX</t>
+          <t>3304C-d11.7</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>VERGNANO</t>
+          <t>ILIX</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>FH700SE</t>
+          <t>3304C-ILLICO</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -663,11 +688,11 @@
       </c>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="n">
-        <v>20</v>
+        <v>11.7</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>h10</t>
+          <t>e8</t>
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
@@ -684,16 +709,18 @@
       <c r="O2" t="b">
         <v>1</v>
       </c>
-      <c r="P2" t="inlineStr"/>
+      <c r="P2" t="n">
+        <v>26</v>
+      </c>
       <c r="Q2" t="n">
         <v>26</v>
       </c>
       <c r="R2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>HA-20</t>
+          <t>HA-12</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -707,33 +734,43 @@
         </is>
       </c>
       <c r="V2" t="inlineStr"/>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>h6</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr"/>
-      <c r="Y2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>HSS-Co8</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>HSS-Co8</t>
+        </is>
+      </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>V-MAXX</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr"/>
+          <t>TiCN</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>DIN 1835/1 / DIN 327</t>
+        </is>
+      </c>
       <c r="AB2" t="n">
         <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="AD2" t="n">
-        <v>92</v>
+        <v>110</v>
       </c>
       <c r="AE2" t="inlineStr"/>
       <c r="AF2" t="n">
-        <v>38</v>
-      </c>
-      <c r="AG2" t="inlineStr"/>
+        <v>30</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>10</v>
+      </c>
       <c r="AH2" t="inlineStr"/>
       <c r="AI2" t="inlineStr"/>
       <c r="AJ2" t="inlineStr"/>
@@ -743,25 +780,36 @@
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>2022/Vergnano-End-Mills-Catalogue-65.pdf</t>
+          <t>2021/Ilix-illico-ITeh.pdf</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>VHM</t>
+          <t>HSS</t>
         </is>
       </c>
       <c r="AO2" t="b">
         <v>0</v>
       </c>
       <c r="AP2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AQ2" t="n">
         <v>1</v>
+      </c>
+      <c r="AR2" t="inlineStr"/>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="inlineStr"/>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>PMK</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>EU464050</t>
+          <t>E5425050</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -771,53 +819,51 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>EU464</t>
+          <t>E5425</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
+          <t>MN</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" t="n">
         <v>5</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>e8</t>
+          <t>h10</t>
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+      <c r="J3" t="n">
+        <v>5</v>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O3" t="b">
         <v>1</v>
       </c>
       <c r="P3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>HB-6</t>
+          <t>HA-5</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -827,7 +873,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>HA</t>
         </is>
       </c>
       <c r="V3" t="inlineStr"/>
@@ -836,34 +882,30 @@
           <t>h6</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr"/>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>HSS-Co8</t>
-        </is>
-      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Micro Grain Carbide</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr"/>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>HARDSLICK</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>DIN 844</t>
-        </is>
-      </c>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr"/>
       <c r="AB3" t="n">
         <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AD3" t="n">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="AE3" t="inlineStr"/>
       <c r="AF3" t="n">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="AG3" t="inlineStr"/>
       <c r="AH3" t="inlineStr"/>
@@ -875,12 +917,12 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>2021/YG1-TOOLING</t>
+          <t>2017 - YG1 - General catalogue</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>HSS</t>
+          <t>VHM</t>
         </is>
       </c>
       <c r="AO3" t="b">
@@ -888,58 +930,87 @@
       </c>
       <c r="AP3" t="b">
         <v>0</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>3</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>19.63</v>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AT3" t="n">
+        <v>1804.66</v>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>MN</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>9114801202</t>
+          <t>C2MSD0480</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>HELION</t>
+          <t>MITSUBISHI</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>91.1480</t>
+          <t>C2MS</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>PKMS</t>
+          <t>PMNS</t>
         </is>
       </c>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
-        <v>12</v>
-      </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
+        <v>4.8</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0/-0,02</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="n">
-        <v>0.35</v>
-      </c>
+      <c r="L4" t="inlineStr"/>
       <c r="M4" t="n">
-        <v>26</v>
-      </c>
-      <c r="N4" t="inlineStr"/>
+        <v>13</v>
+      </c>
+      <c r="N4" t="n">
+        <v>13</v>
+      </c>
       <c r="O4" t="b">
         <v>1</v>
       </c>
-      <c r="P4" t="inlineStr"/>
+      <c r="P4" t="n">
+        <v>13</v>
+      </c>
       <c r="Q4" t="n">
-        <v>38</v>
+        <v>13</v>
       </c>
       <c r="R4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>HA-12</t>
+          <t>HA-6</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -958,25 +1029,23 @@
       <c r="Y4" t="inlineStr"/>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>AlCrN</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>HELION NORM</t>
-        </is>
-      </c>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr"/>
       <c r="AB4" t="n">
         <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="AD4" t="n">
-        <v>83</v>
+        <v>50</v>
       </c>
       <c r="AE4" t="inlineStr"/>
-      <c r="AF4" t="inlineStr"/>
+      <c r="AF4" t="n">
+        <v>30</v>
+      </c>
       <c r="AG4" t="inlineStr"/>
       <c r="AH4" t="inlineStr"/>
       <c r="AI4" t="inlineStr"/>
@@ -987,7 +1056,7 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>2023/HELION_smart_line</t>
+          <t>2020 / Mitsubishi Website</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
@@ -996,66 +1065,83 @@
         </is>
       </c>
       <c r="AO4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP4" t="b">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AR4" t="inlineStr"/>
+      <c r="AS4" t="inlineStr"/>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>PMNS</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>END MILL Ø11 FA405E V-MAXX</t>
+          <t>ESE94010002025</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>VERGNANO</t>
+          <t>YG1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>FA405E</t>
+          <t>ESE94</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>PMK</t>
+          <t>H</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>h10</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
+          <t>0/-0,01</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>-0.01</v>
+      </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+      <c r="J5" t="n">
+        <v>1</v>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="N5" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="O5" t="b">
         <v>1</v>
       </c>
-      <c r="P5" t="inlineStr"/>
+      <c r="P5" t="n">
+        <v>1</v>
+      </c>
       <c r="Q5" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="R5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>HA-12</t>
+          <t>HA-4</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1076,32 +1162,28 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>HSSY</t>
+          <t>CBN</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr"/>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>V-MAXX</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>DIN 844 K</t>
-        </is>
-      </c>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr"/>
       <c r="AB5" t="n">
         <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="AD5" t="n">
-        <v>79</v>
+        <v>50</v>
       </c>
       <c r="AE5" t="inlineStr"/>
       <c r="AF5" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="inlineStr"/>
       <c r="AH5" t="inlineStr"/>
@@ -1113,12 +1195,12 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>2022/Vergnano-End-Mills-Catalogue-65.pdf</t>
+          <t>2020: www.yg1.co.kr/toolselection/main/</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>PME</t>
+          <t>CBN</t>
         </is>
       </c>
       <c r="AO5" t="b">
@@ -1126,32 +1208,43 @@
       </c>
       <c r="AP5" t="b">
         <v>0</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>3</v>
+      </c>
+      <c r="AR5" t="inlineStr"/>
+      <c r="AS5" t="inlineStr"/>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M34F-100R000TP</t>
+          <t>3300C-d19</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>OSCAR</t>
+          <t>ILIX</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>M34F/TP</t>
+          <t>3300C-ILLICO</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>PMK</t>
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1160,32 +1253,30 @@
       </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="n">
-        <v>10</v>
-      </c>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="n">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="N6" t="n">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="O6" t="b">
         <v>1</v>
       </c>
       <c r="P6" t="n">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="Q6" t="n">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="R6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>HA-10</t>
+          <t>HA-16</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1199,33 +1290,43 @@
         </is>
       </c>
       <c r="V6" t="inlineStr"/>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>h6</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr"/>
-      <c r="Y6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>HSS-Co8</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>HSS-Co8</t>
+        </is>
+      </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr"/>
+          <t>TiCN</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>DIN 1835/1 / DIN 327</t>
+        </is>
+      </c>
       <c r="AB6" t="n">
         <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="AD6" t="n">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="n">
         <v>30</v>
       </c>
-      <c r="AG6" t="inlineStr"/>
+      <c r="AG6" t="n">
+        <v>10</v>
+      </c>
       <c r="AH6" t="inlineStr"/>
       <c r="AI6" t="inlineStr"/>
       <c r="AJ6" t="inlineStr"/>
@@ -1235,12 +1336,12 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t xml:space="preserve">2014 / OSCAR каталог RU </t>
+          <t>2021/Ilix-illico-ITeh.pdf</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>VHM</t>
+          <t>HSS</t>
         </is>
       </c>
       <c r="AO6" t="b">
@@ -1248,6 +1349,17 @@
       </c>
       <c r="AP6" t="b">
         <v>0</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR6" t="inlineStr"/>
+      <c r="AS6" t="inlineStr"/>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>PMK</t>
+        </is>
       </c>
     </row>
   </sheetData>
